--- a/Data/EXCEL/Transfer/salemon/202412/1592-salemon-202412.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202412/1592-salemon-202412.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\xls2xlsx\202412\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202412\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5296DE29-2C0B-46A3-90B3-056EF6B9D3AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D60405AC-E4CB-43E8-B4C6-C6D779F57F97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{03AE1B39-A8D4-46CD-8755-BF63A31D4DBC}"/>
+    <workbookView xWindow="2235" yWindow="1695" windowWidth="21600" windowHeight="13425" xr2:uid="{9A578229-A4F2-45C1-B0C1-1609506A379E}"/>
   </bookViews>
   <sheets>
     <sheet name="1592-salemon-202412" sheetId="2" r:id="rId1"/>
@@ -1258,22 +1258,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F125CF4-7F47-4552-A208-54226AAE0E37}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2467058A-A9B8-46FB-B4E0-61EF13E2C71C}">
   <dimension ref="A1:Q8"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="7" width="13.54296875" customWidth="1"/>
-    <col min="8" max="8" width="16.453125" customWidth="1"/>
-    <col min="9" max="9" width="18.6328125" customWidth="1"/>
-    <col min="10" max="12" width="13.54296875" customWidth="1"/>
-    <col min="13" max="13" width="16.453125" customWidth="1"/>
-    <col min="14" max="14" width="18.6328125" customWidth="1"/>
-    <col min="15" max="16" width="13.54296875" customWidth="1"/>
-    <col min="17" max="17" width="14.7265625" customWidth="1"/>
+    <col min="1" max="1" width="10.875" customWidth="1"/>
+    <col min="2" max="7" width="8.875" customWidth="1"/>
+    <col min="8" max="8" width="10.625" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="12" width="8.875" customWidth="1"/>
+    <col min="13" max="13" width="10.625" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
+    <col min="15" max="16" width="8.875" customWidth="1"/>
+    <col min="17" max="17" width="9.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -1300,7 +1300,7 @@
       <c r="P1" s="20"/>
       <c r="Q1" s="21"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="17"/>
       <c r="B2" s="16" t="s">
         <v>4</v>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="Q2" s="21"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="17"/>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
@@ -1382,7 +1382,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="18"/>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -1421,7 +1421,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>44531</v>
       </c>
@@ -1474,7 +1474,7 @@
         <v>-84</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>44501</v>
       </c>
@@ -1527,7 +1527,7 @@
         <v>-83.4</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>44470</v>
       </c>
@@ -1580,7 +1580,7 @@
         <v>-81.8</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>44440</v>
       </c>
